--- a/complaint_forms/029_health_outreach_complaint_form--complaint_forms.xlsx
+++ b/complaint_forms/029_health_outreach_complaint_form--complaint_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -776,12 +776,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'staff'}</t>
+          <t>staff</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Staff'}</t>
+          <t>Staff</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'nurse'}</t>
+          <t>nurse</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Nurse'}</t>
+          <t>Nurse</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'scheduled'}</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Scheduled'}</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_scheduled'}</t>
+          <t>not_scheduled</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Not Scheduled'}</t>
+          <t>Not Scheduled</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -979,29 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'chatjimmy'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'chatjimmy'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>assigned_to_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'chatjimmy'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'chatjimmy'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
